--- a/marketer_forms/003_facebook_fan_page_setup_request_form--marketer_forms.xlsx
+++ b/marketer_forms/003_facebook_fan_page_setup_request_form--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1211,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
